--- a/Listing/BFD05D.xlsx
+++ b/Listing/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="716">
   <si>
     <t/>
   </si>
@@ -31,96 +31,84 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20035489</t>
-  </si>
-  <si>
-    <t>LA FONTE FTTUCINE225</t>
+    <t>10004331</t>
+  </si>
+  <si>
+    <t>LA FONTE SPGHT 450G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20117918</t>
+  </si>
+  <si>
+    <t>LA FONTE LASAGNA 230</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10027768</t>
+  </si>
+  <si>
+    <t>L/F SPAG SAUS BLG117</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10016520</t>
+  </si>
+  <si>
+    <t>PAZTO MAKARN KEJU 63</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20039011</t>
+  </si>
+  <si>
+    <t>MMSUKA S.KRM AYM 55G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10004331</t>
-  </si>
-  <si>
-    <t>LA FONTE SPGHT 450G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20117918</t>
-  </si>
-  <si>
-    <t>LA FONTE LASAGNA 230</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10027952</t>
-  </si>
-  <si>
-    <t>L/F SPAG.SAUS AYM117</t>
+    <t>20137017</t>
+  </si>
+  <si>
+    <t>DLMONTE CRBNARA 180G</t>
+  </si>
+  <si>
+    <t>20039621</t>
+  </si>
+  <si>
+    <t>PRONAS SC BOLG SP315</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20066050</t>
+  </si>
+  <si>
+    <t>DELMONTE SPG.SAUS250</t>
+  </si>
+  <si>
+    <t>20066052</t>
+  </si>
+  <si>
+    <t>DLMONTE BBQ.SAUS 250</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10027768</t>
-  </si>
-  <si>
-    <t>L/F SPAG SAUS BLG117</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10016520</t>
-  </si>
-  <si>
-    <t>PAZTO MAKARN KEJU 63</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20039011</t>
-  </si>
-  <si>
-    <t>MMSUKA S.KRM AYM 55G</t>
-  </si>
-  <si>
-    <t>20137017</t>
-  </si>
-  <si>
-    <t>DLMONTE CRBNARA 180G</t>
-  </si>
-  <si>
-    <t>20039621</t>
-  </si>
-  <si>
-    <t>PRONAS SC BOLG SP315</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20066050</t>
-  </si>
-  <si>
-    <t>DELMONTE SPG.SAUS250</t>
-  </si>
-  <si>
-    <t>20066052</t>
-  </si>
-  <si>
-    <t>DLMONTE BBQ.SAUS 250</t>
-  </si>
-  <si>
     <t>20024512</t>
   </si>
   <si>
@@ -190,7 +178,7 @@
     <t>10035900</t>
   </si>
   <si>
-    <t>A/SAJIKU TPG SRB 220</t>
+    <t>A/SAJIKU TPG SRB 210</t>
   </si>
   <si>
     <t>20014694</t>
@@ -346,88 +334,136 @@
     <t>PRONAS NS GRG SP 110</t>
   </si>
   <si>
+    <t>20059859</t>
+  </si>
+  <si>
+    <t>KOBE BMB N/GRG PDS20</t>
+  </si>
+  <si>
+    <t>20098663</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 40G</t>
+  </si>
+  <si>
+    <t>20103449</t>
+  </si>
+  <si>
+    <t>SAJIKU NSI GRG SPL20</t>
+  </si>
+  <si>
+    <t>20134777</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG ORI 40</t>
+  </si>
+  <si>
+    <t>20134778</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG PDS 40</t>
+  </si>
+  <si>
+    <t>10007775</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.AY20</t>
+  </si>
+  <si>
+    <t>10035898</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 100GR</t>
+  </si>
+  <si>
+    <t>10035899</t>
+  </si>
+  <si>
+    <t>A/MASAKO SAPI 100GR</t>
+  </si>
+  <si>
+    <t>20104719</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 80G</t>
+  </si>
+  <si>
+    <t>20136397</t>
+  </si>
+  <si>
+    <t>KB BMB AYM LNGKS 80G</t>
+  </si>
+  <si>
+    <t>20136577</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB PRLDK 50G</t>
+  </si>
+  <si>
+    <t>20138072</t>
+  </si>
+  <si>
+    <t>RASA/M OPOR AYAM 40G</t>
+  </si>
+  <si>
+    <t>10013821</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.PD20</t>
+  </si>
+  <si>
+    <t>20038549</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 250GR</t>
+  </si>
+  <si>
+    <t>20057290</t>
+  </si>
+  <si>
+    <t>SASA BU AYAM KNG 25G</t>
+  </si>
+  <si>
+    <t>20135316</t>
+  </si>
+  <si>
+    <t>LARISST BMB JMR 40G</t>
+  </si>
+  <si>
+    <t>20136743</t>
+  </si>
+  <si>
+    <t>TDUNG BMB NP.RDNG 27</t>
+  </si>
+  <si>
+    <t>20137258</t>
+  </si>
+  <si>
+    <t>RASA/M GULAI AYAM40G</t>
+  </si>
+  <si>
+    <t>20138371</t>
+  </si>
+  <si>
+    <t>MAGGI MAGIC LZT 80G</t>
+  </si>
+  <si>
     <t>10013823</t>
   </si>
   <si>
     <t>A/SAJIKU BB.AYM GR24</t>
   </si>
   <si>
-    <t>10035898</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 100GR</t>
-  </si>
-  <si>
-    <t>20057290</t>
-  </si>
-  <si>
-    <t>SASA BU AYAM KNG 25G</t>
-  </si>
-  <si>
-    <t>20098663</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 40G</t>
-  </si>
-  <si>
-    <t>20134777</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG ORI 40</t>
-  </si>
-  <si>
-    <t>20134778</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG PDS 40</t>
-  </si>
-  <si>
-    <t>20136577</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB PRLDK 50G</t>
-  </si>
-  <si>
-    <t>10035899</t>
-  </si>
-  <si>
-    <t>A/MASAKO SAPI 100GR</t>
-  </si>
-  <si>
     <t>20025563</t>
   </si>
   <si>
     <t>SASA BMB LUMUR AYM26</t>
   </si>
   <si>
-    <t>20059859</t>
-  </si>
-  <si>
-    <t>KOBE BMB N/GRG PDS20</t>
-  </si>
-  <si>
-    <t>20103449</t>
-  </si>
-  <si>
-    <t>SAJIKU NSI GRG SPL20</t>
-  </si>
-  <si>
-    <t>20104719</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 80G</t>
-  </si>
-  <si>
-    <t>20136743</t>
-  </si>
-  <si>
-    <t>TDUNG BMB NP.RDNG 27</t>
-  </si>
-  <si>
-    <t>20138072</t>
-  </si>
-  <si>
-    <t>RASA/M OPOR AYAM 40G</t>
+    <t>20038548</t>
+  </si>
+  <si>
+    <t>MASAKO SAPI 250GR</t>
   </si>
   <si>
     <t>20134507</t>
@@ -436,54 +472,6 @@
     <t>TUDUNG BMB NS UDUK27</t>
   </si>
   <si>
-    <t>20135316</t>
-  </si>
-  <si>
-    <t>LARISST BMB JMR 40G</t>
-  </si>
-  <si>
-    <t>20136397</t>
-  </si>
-  <si>
-    <t>KB BMB AYM LNGKS 80G</t>
-  </si>
-  <si>
-    <t>20137258</t>
-  </si>
-  <si>
-    <t>RASA/M GULAI AYAM40G</t>
-  </si>
-  <si>
-    <t>20138371</t>
-  </si>
-  <si>
-    <t>MAGGI MAGIC LZT 80G</t>
-  </si>
-  <si>
-    <t>10007775</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.AY20</t>
-  </si>
-  <si>
-    <t>10013821</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.PD20</t>
-  </si>
-  <si>
-    <t>20038548</t>
-  </si>
-  <si>
-    <t>MASAKO SAPI 250GR</t>
-  </si>
-  <si>
-    <t>20038549</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 250GR</t>
-  </si>
-  <si>
     <t>20138843</t>
   </si>
   <si>
@@ -538,12 +526,6 @@
     <t>SAORI SAUS LD HTM133</t>
   </si>
   <si>
-    <t>20129757</t>
-  </si>
-  <si>
-    <t>SAORI SS BULGOGI 133</t>
-  </si>
-  <si>
     <t>20044599</t>
   </si>
   <si>
@@ -577,615 +559,603 @@
     <t>14</t>
   </si>
   <si>
-    <t>20098776</t>
-  </si>
-  <si>
-    <t>MS SS.TIRAM UDG&amp;J260</t>
+    <t>20015850</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 275</t>
+  </si>
+  <si>
+    <t>20027097</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMBL EXT275</t>
+  </si>
+  <si>
+    <t>20115489</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMB DHSY275</t>
+  </si>
+  <si>
+    <t>20027096</t>
+  </si>
+  <si>
+    <t>INDOFOOD SAUS TMT275</t>
+  </si>
+  <si>
+    <t>20064412</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL ASLI 270</t>
+  </si>
+  <si>
+    <t>20063027</t>
+  </si>
+  <si>
+    <t>ABC SMBL EXT.PDS 270</t>
+  </si>
+  <si>
+    <t>20132492</t>
+  </si>
+  <si>
+    <t>ABC SBL EXTRM PDS270</t>
+  </si>
+  <si>
+    <t>10000116</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL BTL 335ML</t>
+  </si>
+  <si>
+    <t>10003362</t>
+  </si>
+  <si>
+    <t>ABC SBL.EXT PEDAS335</t>
+  </si>
+  <si>
+    <t>10013041</t>
+  </si>
+  <si>
+    <t>INDO/F SAMBAL E/P335</t>
+  </si>
+  <si>
+    <t>10012917</t>
+  </si>
+  <si>
+    <t>INDO/F SMBAL BGK 335</t>
+  </si>
+  <si>
+    <t>20036241</t>
+  </si>
+  <si>
+    <t>2BLIBIS SAUS CABE335</t>
+  </si>
+  <si>
+    <t>20036344</t>
+  </si>
+  <si>
+    <t>2BLIBIS SAUS CABE135</t>
+  </si>
+  <si>
+    <t>10000212</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL 130ML</t>
+  </si>
+  <si>
+    <t>10036708</t>
+  </si>
+  <si>
+    <t>ABC SBL.EXT PEDAS130</t>
+  </si>
+  <si>
+    <t>10000320</t>
+  </si>
+  <si>
+    <t>ABC SAUCE TOMAT130ML</t>
+  </si>
+  <si>
+    <t>20115632</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMB DHSY135</t>
+  </si>
+  <si>
+    <t>20010272</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMB EXT 135</t>
+  </si>
+  <si>
+    <t>10002989</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 135</t>
+  </si>
+  <si>
+    <t>20009269</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 135</t>
+  </si>
+  <si>
+    <t>20036194</t>
+  </si>
+  <si>
+    <t>DELMONTE KETCHUP 135</t>
+  </si>
+  <si>
+    <t>20091863</t>
+  </si>
+  <si>
+    <t>MMSUKA HOT LAVA 130</t>
+  </si>
+  <si>
+    <t>20091864</t>
+  </si>
+  <si>
+    <t>MMSUKA HOT LAVA 260</t>
+  </si>
+  <si>
+    <t>20141501</t>
+  </si>
+  <si>
+    <t>2 BELIBIS PDS LD 235</t>
+  </si>
+  <si>
+    <t>20141500</t>
+  </si>
+  <si>
+    <t>2 BELIBIS EX/PDS 235</t>
+  </si>
+  <si>
+    <t>20132660</t>
+  </si>
+  <si>
+    <t>2 BELIBIS SAUS 235ML</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20015850</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 275</t>
-  </si>
-  <si>
-    <t>20027097</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMBL EXT275</t>
-  </si>
-  <si>
-    <t>20115489</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB DHSY275</t>
-  </si>
-  <si>
-    <t>20027096</t>
-  </si>
-  <si>
-    <t>INDOFOOD SAUS TMT275</t>
-  </si>
-  <si>
-    <t>20064412</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL ASLI 270</t>
-  </si>
-  <si>
-    <t>20063027</t>
-  </si>
-  <si>
-    <t>ABC SMBL EXT.PDS 270</t>
-  </si>
-  <si>
-    <t>20132492</t>
-  </si>
-  <si>
-    <t>ABC SBL EXTRM PDS270</t>
-  </si>
-  <si>
-    <t>10000116</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL BTL 335ML</t>
-  </si>
-  <si>
-    <t>10003362</t>
-  </si>
-  <si>
-    <t>ABC SBL.EXT PEDAS335</t>
-  </si>
-  <si>
-    <t>10013041</t>
-  </si>
-  <si>
-    <t>INDO/F SAMBAL E/P335</t>
-  </si>
-  <si>
-    <t>10012917</t>
-  </si>
-  <si>
-    <t>INDO/F SMBAL BGK 335</t>
-  </si>
-  <si>
-    <t>20036241</t>
-  </si>
-  <si>
-    <t>2BLIBIS SAUS CABE335</t>
-  </si>
-  <si>
-    <t>10004367</t>
-  </si>
-  <si>
-    <t>SASA SAMBAL ASLI 135</t>
-  </si>
-  <si>
-    <t>20036344</t>
-  </si>
-  <si>
-    <t>2BLIBIS SAUS CABE135</t>
-  </si>
-  <si>
-    <t>10000212</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL 130ML</t>
-  </si>
-  <si>
-    <t>10036708</t>
-  </si>
-  <si>
-    <t>ABC SBL.EXT PEDAS130</t>
-  </si>
-  <si>
-    <t>10000320</t>
-  </si>
-  <si>
-    <t>ABC SAUCE TOMAT130ML</t>
-  </si>
-  <si>
-    <t>20115632</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB DHSY135</t>
-  </si>
-  <si>
-    <t>20010272</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB EXT 135</t>
-  </si>
-  <si>
-    <t>10002989</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 135</t>
-  </si>
-  <si>
-    <t>20009269</t>
-  </si>
-  <si>
-    <t>DELMONTE EXT.HOT 135</t>
-  </si>
-  <si>
-    <t>20036194</t>
-  </si>
-  <si>
-    <t>DELMONTE KETCHUP 135</t>
-  </si>
-  <si>
-    <t>20091863</t>
-  </si>
-  <si>
-    <t>MMSUKA HOT LAVA 130</t>
-  </si>
-  <si>
-    <t>20091864</t>
-  </si>
-  <si>
-    <t>MMSUKA HOT LAVA 260</t>
-  </si>
-  <si>
-    <t>20132660</t>
-  </si>
-  <si>
-    <t>2 BELIBIS SAUS 235ML</t>
+    <t>20082351</t>
+  </si>
+  <si>
+    <t>DELM.SAOS TOMATO 265</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>20082351</t>
-  </si>
-  <si>
-    <t>DELM.SAOS TOMATO 265</t>
+    <t>10027529</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 265</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>10027529</t>
-  </si>
-  <si>
-    <t>DELMONTE EXT.HOT 265</t>
+    <t>20139356</t>
+  </si>
+  <si>
+    <t>ABC BMBU KCG 180G</t>
+  </si>
+  <si>
+    <t>20034315</t>
+  </si>
+  <si>
+    <t>ABC SMBAL TERASI 180</t>
+  </si>
+  <si>
+    <t>20043799</t>
+  </si>
+  <si>
+    <t>ABC SMBL EXT PDS 380</t>
+  </si>
+  <si>
+    <t>20104152</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 200</t>
+  </si>
+  <si>
+    <t>20009270</t>
+  </si>
+  <si>
+    <t>DELMONTE KTCHUP 24'S</t>
+  </si>
+  <si>
+    <t>20009268</t>
+  </si>
+  <si>
+    <t>DELMONTE SAMBL 24X8</t>
+  </si>
+  <si>
+    <t>20135428</t>
+  </si>
+  <si>
+    <t>KOBE BMB RNDANG 3X20</t>
+  </si>
+  <si>
+    <t>10031438</t>
+  </si>
+  <si>
+    <t>SASA SMB X.HOT 24X8G</t>
+  </si>
+  <si>
+    <t>20036865</t>
+  </si>
+  <si>
+    <t>ABC SMAL TERASI 10'S</t>
+  </si>
+  <si>
+    <t>20054028</t>
+  </si>
+  <si>
+    <t>INDO/F SMBL BLDO 200</t>
+  </si>
+  <si>
+    <t>20048582</t>
+  </si>
+  <si>
+    <t>FINNA SMBL/T ULG 10S</t>
+  </si>
+  <si>
+    <t>20012187</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 24S</t>
+  </si>
+  <si>
+    <t>20133690</t>
+  </si>
+  <si>
+    <t>SEDAAP KALDU AYAM250</t>
+  </si>
+  <si>
+    <t>20133691</t>
+  </si>
+  <si>
+    <t>SEDAAP KALDU SAPI250</t>
+  </si>
+  <si>
+    <t>20129197</t>
+  </si>
+  <si>
+    <t>KOBE BMB NS UDK 3X15</t>
+  </si>
+  <si>
+    <t>20135466</t>
+  </si>
+  <si>
+    <t>KOBE BMB NS KNNG3X15</t>
+  </si>
+  <si>
+    <t>20128243</t>
+  </si>
+  <si>
+    <t>M/S GIM BORI PDS 25G</t>
+  </si>
+  <si>
+    <t>20128242</t>
+  </si>
+  <si>
+    <t>M/S GIM BORI ORG 25G</t>
+  </si>
+  <si>
+    <t>20042089</t>
+  </si>
+  <si>
+    <t>KOBE BONCABE ORG 45G</t>
+  </si>
+  <si>
+    <t>20074334</t>
+  </si>
+  <si>
+    <t>KOBE BONCABE L30 40G</t>
+  </si>
+  <si>
+    <t>20047809</t>
+  </si>
+  <si>
+    <t>KOBE BONCABE L15 45G</t>
+  </si>
+  <si>
+    <t>20117663</t>
+  </si>
+  <si>
+    <t>BONCABE LV50 MAX 30G</t>
+  </si>
+  <si>
+    <t>20115355</t>
+  </si>
+  <si>
+    <t>BONCABE NORI LVL 2</t>
+  </si>
+  <si>
+    <t>20056800</t>
+  </si>
+  <si>
+    <t>LADAKU MRC BBK BTL35</t>
+  </si>
+  <si>
+    <t>10036773</t>
+  </si>
+  <si>
+    <t>KUPU2 LADA PTH BBK85</t>
+  </si>
+  <si>
+    <t>10036774</t>
+  </si>
+  <si>
+    <t>KUPU2 LADA HTM BBK83</t>
+  </si>
+  <si>
+    <t>20134371</t>
+  </si>
+  <si>
+    <t>IDM CABE MRH BBK 50G</t>
+  </si>
+  <si>
+    <t>20134372</t>
+  </si>
+  <si>
+    <t>IDM BWG PTIH BBK 60G</t>
+  </si>
+  <si>
+    <t>20134248</t>
+  </si>
+  <si>
+    <t>IDM KETUMBAR BBK 50G</t>
+  </si>
+  <si>
+    <t>20134247</t>
+  </si>
+  <si>
+    <t>IDM LADA PTH BBK 50G</t>
+  </si>
+  <si>
+    <t>20134249</t>
+  </si>
+  <si>
+    <t>IDM KUNYIT BBK 50G</t>
+  </si>
+  <si>
+    <t>10002765</t>
+  </si>
+  <si>
+    <t>INDOFOOD RENDANG 50G</t>
+  </si>
+  <si>
+    <t>10005820</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU AYAM 94G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20013341</t>
+  </si>
+  <si>
+    <t>BAMBOE RENDANG 35G</t>
+  </si>
+  <si>
+    <t>20013345</t>
+  </si>
+  <si>
+    <t>BAMBOE NASI GRG 40G</t>
+  </si>
+  <si>
+    <t>20036783</t>
+  </si>
+  <si>
+    <t>INDOFD RCK IKN GRG20</t>
+  </si>
+  <si>
+    <t>20139390</t>
+  </si>
+  <si>
+    <t>INDO RACIK BALADO 55</t>
+  </si>
+  <si>
+    <t>20139801</t>
+  </si>
+  <si>
+    <t>ROYCO RENDANG 45G</t>
+  </si>
+  <si>
+    <t>10002767</t>
+  </si>
+  <si>
+    <t>INDOFOOD GULAI 45G</t>
+  </si>
+  <si>
+    <t>10002768</t>
+  </si>
+  <si>
+    <t>INDOFOOD OPOR AYM 45</t>
+  </si>
+  <si>
+    <t>10040150</t>
+  </si>
+  <si>
+    <t>INDOF/TBR BK BBQ 25G</t>
+  </si>
+  <si>
+    <t>20014281</t>
+  </si>
+  <si>
+    <t>INDOF RACIK AYM.GR26</t>
+  </si>
+  <si>
+    <t>20021359</t>
+  </si>
+  <si>
+    <t>BAMBOE SOTO MADURA40</t>
+  </si>
+  <si>
+    <t>20084470</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU SAPI 220</t>
+  </si>
+  <si>
+    <t>20133255</t>
+  </si>
+  <si>
+    <t>INDOFOOD AYM MNTGA50</t>
+  </si>
+  <si>
+    <t>20139784</t>
+  </si>
+  <si>
+    <t>ROYCO SOTO AYAM 40G</t>
+  </si>
+  <si>
+    <t>10002915</t>
+  </si>
+  <si>
+    <t>INDOFOOD SOTO AYM45G</t>
+  </si>
+  <si>
+    <t>10036780</t>
+  </si>
+  <si>
+    <t>INDOFOOD KARE 45G</t>
+  </si>
+  <si>
+    <t>10040157</t>
+  </si>
+  <si>
+    <t>INDOF TBR BK KEJU25G</t>
+  </si>
+  <si>
+    <t>20013617</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK S.ASM33</t>
+  </si>
+  <si>
+    <t>20023890</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK S.SOP20</t>
+  </si>
+  <si>
+    <t>20077364</t>
+  </si>
+  <si>
+    <t>BAMBOE BMB TOM YUM60</t>
+  </si>
+  <si>
+    <t>20084469</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU AYAM 220</t>
+  </si>
+  <si>
+    <t>20139802</t>
+  </si>
+  <si>
+    <t>ROYCO OPOR AYAM 45G</t>
+  </si>
+  <si>
+    <t>10002766</t>
+  </si>
+  <si>
+    <t>INDOFOOD RAWON 50G</t>
+  </si>
+  <si>
+    <t>20013333</t>
+  </si>
+  <si>
+    <t>BAMBOE BUMBU RAWON54</t>
+  </si>
+  <si>
+    <t>20013616</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK N.GRG20</t>
+  </si>
+  <si>
+    <t>20113574</t>
+  </si>
+  <si>
+    <t>INDF RCK NSGOR SS 3S</t>
+  </si>
+  <si>
+    <t>20133254</t>
+  </si>
+  <si>
+    <t>INDOFOOD SEMUR 50G</t>
+  </si>
+  <si>
+    <t>20140677</t>
+  </si>
+  <si>
+    <t>IND TABURI GAS PD 25</t>
+  </si>
+  <si>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
+  </si>
+  <si>
+    <t>20101461</t>
+  </si>
+  <si>
+    <t>ABC KECAP MANIS 825G</t>
+  </si>
+  <si>
+    <t>20123088</t>
+  </si>
+  <si>
+    <t>SEDAAP KCP MNS 720ML</t>
+  </si>
+  <si>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
+  </si>
+  <si>
+    <t>20019249</t>
+  </si>
+  <si>
+    <t>SEDAAP KECAP PCH700G</t>
+  </si>
+  <si>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
+  </si>
+  <si>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 700G</t>
+  </si>
+  <si>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 735</t>
+  </si>
+  <si>
+    <t>20134927</t>
+  </si>
+  <si>
+    <t>SEDAP KCP MNS 270G</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20139356</t>
-  </si>
-  <si>
-    <t>ABC BMBU KCG 180G</t>
-  </si>
-  <si>
-    <t>20034315</t>
-  </si>
-  <si>
-    <t>ABC SMBAL TERASI 180</t>
-  </si>
-  <si>
-    <t>20043799</t>
-  </si>
-  <si>
-    <t>ABC SMBL EXT PDS 380</t>
-  </si>
-  <si>
-    <t>20104152</t>
-  </si>
-  <si>
-    <t>DELMONTE EXT.HOT 200</t>
-  </si>
-  <si>
-    <t>20009270</t>
-  </si>
-  <si>
-    <t>DELMONTE KTCHUP 24'S</t>
-  </si>
-  <si>
-    <t>20009268</t>
-  </si>
-  <si>
-    <t>DELMONTE SAMBL 24X8</t>
-  </si>
-  <si>
-    <t>20135428</t>
-  </si>
-  <si>
-    <t>KOBE BMB RNDANG 3X20</t>
-  </si>
-  <si>
-    <t>10031438</t>
-  </si>
-  <si>
-    <t>SASA SMB X.HOT 24X8G</t>
-  </si>
-  <si>
-    <t>20036865</t>
-  </si>
-  <si>
-    <t>ABC SMAL TERASI 10'S</t>
-  </si>
-  <si>
-    <t>20054028</t>
-  </si>
-  <si>
-    <t>INDO/F SMBL BLDO 200</t>
-  </si>
-  <si>
-    <t>20048582</t>
-  </si>
-  <si>
-    <t>FINNA SMBL/T ULG 10S</t>
-  </si>
-  <si>
-    <t>20012187</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 24S</t>
-  </si>
-  <si>
-    <t>20133690</t>
-  </si>
-  <si>
-    <t>SEDAAP KALDU AYAM250</t>
-  </si>
-  <si>
-    <t>20133691</t>
-  </si>
-  <si>
-    <t>SEDAAP KALDU SAPI250</t>
-  </si>
-  <si>
-    <t>20129197</t>
-  </si>
-  <si>
-    <t>KOBE BMB NS UDK 3X15</t>
-  </si>
-  <si>
-    <t>20135466</t>
-  </si>
-  <si>
-    <t>KOBE BMB NS KNNG3X15</t>
-  </si>
-  <si>
-    <t>20128243</t>
-  </si>
-  <si>
-    <t>M/S GIM BORI PDS 25G</t>
-  </si>
-  <si>
-    <t>20128242</t>
-  </si>
-  <si>
-    <t>M/S GIM BORI ORG 25G</t>
-  </si>
-  <si>
-    <t>20042089</t>
-  </si>
-  <si>
-    <t>KOBE BONCABE ORG 45G</t>
-  </si>
-  <si>
-    <t>20074334</t>
-  </si>
-  <si>
-    <t>KOBE BONCABE L30 40G</t>
-  </si>
-  <si>
-    <t>20047809</t>
-  </si>
-  <si>
-    <t>KOBE BONCABE L15 45G</t>
-  </si>
-  <si>
-    <t>20117663</t>
-  </si>
-  <si>
-    <t>BONCABE LV50 MAX 30G</t>
-  </si>
-  <si>
-    <t>20115355</t>
-  </si>
-  <si>
-    <t>BONCABE NORI LVL 2</t>
-  </si>
-  <si>
-    <t>20056800</t>
-  </si>
-  <si>
-    <t>LADAKU MRC BBK BTL35</t>
-  </si>
-  <si>
-    <t>10036773</t>
-  </si>
-  <si>
-    <t>KUPU2 LADA PTH BBK85</t>
-  </si>
-  <si>
-    <t>10036774</t>
-  </si>
-  <si>
-    <t>KUPU2 LADA HTM BBK83</t>
-  </si>
-  <si>
-    <t>20134371</t>
-  </si>
-  <si>
-    <t>IDM CABE MRH BBK 50G</t>
-  </si>
-  <si>
-    <t>20134372</t>
-  </si>
-  <si>
-    <t>IDM BWG PTIH BBK 60G</t>
-  </si>
-  <si>
-    <t>20134248</t>
-  </si>
-  <si>
-    <t>IDM KETUMBAR BBK 50G</t>
-  </si>
-  <si>
-    <t>20134247</t>
-  </si>
-  <si>
-    <t>IDM LADA PTH BBK 50G</t>
-  </si>
-  <si>
-    <t>20134249</t>
-  </si>
-  <si>
-    <t>IDM KUNYIT BBK 50G</t>
-  </si>
-  <si>
-    <t>10027389</t>
-  </si>
-  <si>
-    <t>INDOFOOD KLD.AYM 100</t>
-  </si>
-  <si>
-    <t>10002765</t>
-  </si>
-  <si>
-    <t>INDOFOOD RENDANG 50G</t>
-  </si>
-  <si>
-    <t>10005820</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU AYAM 94G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20013341</t>
-  </si>
-  <si>
-    <t>BAMBOE RENDANG 35G</t>
-  </si>
-  <si>
-    <t>20013345</t>
-  </si>
-  <si>
-    <t>BAMBOE NASI GRG 40G</t>
-  </si>
-  <si>
-    <t>20036783</t>
-  </si>
-  <si>
-    <t>INDOFD RCK IKN GRG20</t>
-  </si>
-  <si>
-    <t>20139390</t>
-  </si>
-  <si>
-    <t>INDO RACIK BALADO 55</t>
-  </si>
-  <si>
-    <t>20139801</t>
-  </si>
-  <si>
-    <t>ROYCO RENDANG 45G</t>
-  </si>
-  <si>
-    <t>10002767</t>
-  </si>
-  <si>
-    <t>INDOFOOD GULAI 45G</t>
-  </si>
-  <si>
-    <t>10002768</t>
-  </si>
-  <si>
-    <t>INDOFOOD OPOR AYM 45</t>
-  </si>
-  <si>
-    <t>10040150</t>
-  </si>
-  <si>
-    <t>INDOF/TBR BK BBQ 25G</t>
-  </si>
-  <si>
-    <t>20014281</t>
-  </si>
-  <si>
-    <t>INDOF RACIK AYM.GR26</t>
-  </si>
-  <si>
-    <t>20021359</t>
-  </si>
-  <si>
-    <t>BAMBOE SOTO MADURA40</t>
-  </si>
-  <si>
-    <t>20084470</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU SAPI 220</t>
-  </si>
-  <si>
-    <t>20133255</t>
-  </si>
-  <si>
-    <t>INDOFOOD AYM MNTGA50</t>
-  </si>
-  <si>
-    <t>20139784</t>
-  </si>
-  <si>
-    <t>ROYCO SOTO AYAM 40G</t>
-  </si>
-  <si>
-    <t>10002915</t>
-  </si>
-  <si>
-    <t>INDOFOOD SOTO AYM45G</t>
-  </si>
-  <si>
-    <t>10036780</t>
-  </si>
-  <si>
-    <t>INDOFOOD KARE 45G</t>
-  </si>
-  <si>
-    <t>10040157</t>
-  </si>
-  <si>
-    <t>INDOF TBR BK KEJU25G</t>
-  </si>
-  <si>
-    <t>20013617</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK S.ASM33</t>
-  </si>
-  <si>
-    <t>20023890</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK S.SOP20</t>
-  </si>
-  <si>
-    <t>20077364</t>
-  </si>
-  <si>
-    <t>BAMBOE BMB TOM YUM60</t>
-  </si>
-  <si>
-    <t>20084469</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU AYAM 220</t>
-  </si>
-  <si>
-    <t>20139802</t>
-  </si>
-  <si>
-    <t>ROYCO OPOR AYAM 45G</t>
-  </si>
-  <si>
-    <t>10002766</t>
-  </si>
-  <si>
-    <t>INDOFOOD RAWON 50G</t>
-  </si>
-  <si>
-    <t>20013333</t>
-  </si>
-  <si>
-    <t>BAMBOE BUMBU RAWON54</t>
-  </si>
-  <si>
-    <t>20013616</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK N.GRG20</t>
-  </si>
-  <si>
-    <t>20113574</t>
-  </si>
-  <si>
-    <t>INDF RCK NSGOR SS 3S</t>
-  </si>
-  <si>
-    <t>20133254</t>
-  </si>
-  <si>
-    <t>INDOFOOD SEMUR 50G</t>
-  </si>
-  <si>
-    <t>20140677</t>
-  </si>
-  <si>
-    <t>IND TABURI GAS PD 25</t>
-  </si>
-  <si>
-    <t>10022534</t>
-  </si>
-  <si>
-    <t>ABC KCP MNS PCH685G</t>
-  </si>
-  <si>
-    <t>20101461</t>
-  </si>
-  <si>
-    <t>ABC KECAP MANIS 825G</t>
-  </si>
-  <si>
-    <t>20123088</t>
-  </si>
-  <si>
-    <t>SEDAAP KCP MNS 720ML</t>
-  </si>
-  <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725G</t>
-  </si>
-  <si>
-    <t>20019249</t>
-  </si>
-  <si>
-    <t>SEDAAP KECAP PCH700G</t>
-  </si>
-  <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 700G</t>
-  </si>
-  <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 735</t>
-  </si>
-  <si>
-    <t>20132493</t>
-  </si>
-  <si>
-    <t>BANGO KCP MNS HTM550</t>
-  </si>
-  <si>
-    <t>20134927</t>
-  </si>
-  <si>
-    <t>SEDAP KCP MNS 270G</t>
-  </si>
-  <si>
     <t>20064956</t>
   </si>
   <si>
@@ -1453,6 +1423,12 @@
     <t>RT,(E-7.5B)</t>
   </si>
   <si>
+    <t>20069632</t>
+  </si>
+  <si>
+    <t>BOLA/D AGAR MERAH 7G</t>
+  </si>
+  <si>
     <t>20069634</t>
   </si>
   <si>
@@ -1471,108 +1447,108 @@
     <t>SW.GLB AGAR COKL. 7G</t>
   </si>
   <si>
+    <t>10036817</t>
+  </si>
+  <si>
+    <t>SW.GLB AGAR PUTIH 7G</t>
+  </si>
+  <si>
     <t>10036819</t>
   </si>
   <si>
     <t>SW.GLB AGAR MERAH 7G</t>
   </si>
   <si>
-    <t>20069632</t>
-  </si>
-  <si>
-    <t>BOLA/D AGAR MERAH 7G</t>
-  </si>
-  <si>
-    <t>10036817</t>
-  </si>
-  <si>
-    <t>SW.GLB AGAR PUTIH 7G</t>
-  </si>
-  <si>
     <t>10036821</t>
   </si>
   <si>
     <t>SW.GLB AGAR HIJAU 7G</t>
   </si>
   <si>
+    <t>10016716</t>
+  </si>
+  <si>
+    <t>NUTRIJELL PLAIN 15G</t>
+  </si>
+  <si>
+    <t>10016793</t>
+  </si>
+  <si>
+    <t>NUTRIJEL PWD.MELON15</t>
+  </si>
+  <si>
+    <t>20031946</t>
+  </si>
+  <si>
+    <t>NUTRIJELL CINCAU 15G</t>
+  </si>
+  <si>
     <t>20046858</t>
   </si>
   <si>
     <t>NUTRIJEL PWD GRAPE15</t>
   </si>
   <si>
-    <t>10016716</t>
-  </si>
-  <si>
-    <t>NUTRIJELL PLAIN 15G</t>
-  </si>
-  <si>
-    <t>10016793</t>
-  </si>
-  <si>
-    <t>NUTRIJEL PWD.MELON15</t>
-  </si>
-  <si>
-    <t>20031946</t>
-  </si>
-  <si>
-    <t>NUTRIJELL CINCAU 15G</t>
-  </si>
-  <si>
     <t>10016718</t>
   </si>
   <si>
     <t>NUTRIJEL PWD.LECI 15</t>
   </si>
   <si>
+    <t>10016719</t>
+  </si>
+  <si>
+    <t>NUTRIJEL PWD.STRW.15</t>
+  </si>
+  <si>
+    <t>10025449</t>
+  </si>
+  <si>
+    <t>NUTRIJEL POWD.CKT 25</t>
+  </si>
+  <si>
+    <t>20076797</t>
+  </si>
+  <si>
+    <t>NUTRIJELL KLP MD 15G</t>
+  </si>
+  <si>
+    <t>10023618</t>
+  </si>
+  <si>
+    <t>NUTRIJEL PWD.MANGO15</t>
+  </si>
+  <si>
+    <t>20026083</t>
+  </si>
+  <si>
+    <t>AR AGAR PWDR COK 22G</t>
+  </si>
+  <si>
+    <t>20040434</t>
+  </si>
+  <si>
+    <t>MY VLA INST.COKLAT63</t>
+  </si>
+  <si>
     <t>20040435</t>
   </si>
   <si>
     <t>MY VLA INST.VANILA60</t>
   </si>
   <si>
-    <t>20076797</t>
-  </si>
-  <si>
-    <t>NUTRIJELL KLP MD 15G</t>
-  </si>
-  <si>
-    <t>10016719</t>
-  </si>
-  <si>
-    <t>NUTRIJEL PWD.STRW.15</t>
-  </si>
-  <si>
-    <t>10025449</t>
-  </si>
-  <si>
-    <t>NUTRIJEL POWD.CKT 25</t>
-  </si>
-  <si>
-    <t>20040434</t>
-  </si>
-  <si>
-    <t>MY VLA INST.COKLAT63</t>
-  </si>
-  <si>
-    <t>10023618</t>
-  </si>
-  <si>
-    <t>NUTRIJEL PWD.MANGO15</t>
-  </si>
-  <si>
-    <t>20026083</t>
-  </si>
-  <si>
-    <t>AR AGAR PWDR COK 22G</t>
-  </si>
-  <si>
     <t>20134767</t>
   </si>
   <si>
     <t>NUTRIJELL DRK.CHO 24</t>
   </si>
   <si>
+    <t>20141199</t>
+  </si>
+  <si>
+    <t>NUTRIJELL KOPI 20G</t>
+  </si>
+  <si>
     <t>20026090</t>
   </si>
   <si>
@@ -1876,12 +1852,6 @@
     <t>PRO CHIZ SPRD 160G</t>
   </si>
   <si>
-    <t>20091583</t>
-  </si>
-  <si>
-    <t>PRO CHIZ MZRELA 160G</t>
-  </si>
-  <si>
     <t>20069701</t>
   </si>
   <si>
@@ -1918,21 +1888,15 @@
     <t>WINCHEEZ SPREAD 150G</t>
   </si>
   <si>
-    <t>20118903</t>
-  </si>
-  <si>
-    <t>PRO CHIZ GLD CHDR 60</t>
+    <t>20015029</t>
+  </si>
+  <si>
+    <t>KRAFT KEJU CHEDDAR30</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>20015029</t>
-  </si>
-  <si>
-    <t>KRAFT KEJU CHEDDAR30</t>
-  </si>
-  <si>
     <t>10000465</t>
   </si>
   <si>
@@ -1975,6 +1939,12 @@
     <t>EMINA CHS SLC MOZA5S</t>
   </si>
   <si>
+    <t>20141197</t>
+  </si>
+  <si>
+    <t>PRO CHIZ Q.MELT 160G</t>
+  </si>
+  <si>
     <t>20099766</t>
   </si>
   <si>
@@ -2063,6 +2033,12 @@
   </si>
   <si>
     <t>IDM M/GORENG 2L</t>
+  </si>
+  <si>
+    <t>20043943</t>
+  </si>
+  <si>
+    <t>LARISST M/GORENG 2L</t>
   </si>
   <si>
     <t>10012338</t>
@@ -2575,7 +2551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F334"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2682,15 +2658,15 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -2699,10 +2675,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2716,13 +2692,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2736,33 +2712,33 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2776,13 +2752,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2796,13 +2772,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2816,13 +2792,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2836,41 +2812,41 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -2879,10 +2855,10 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2899,10 +2875,10 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2916,13 +2892,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2936,21 +2912,21 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2959,18 +2935,18 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2979,10 +2955,10 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2996,13 +2972,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3016,13 +2992,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3036,13 +3012,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,13 +3032,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3076,13 +3052,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3096,10 +3072,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -3116,13 +3092,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,13 +3112,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3156,13 +3132,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3176,13 +3152,13 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3196,13 +3172,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3216,13 +3192,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3236,13 +3212,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3256,13 +3232,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3276,13 +3252,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3296,53 +3272,53 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3356,133 +3332,133 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3496,13 +3472,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3516,13 +3492,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3536,13 +3512,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3556,13 +3532,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,13 +3552,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,13 +3572,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3616,13 +3592,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3636,13 +3612,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3656,13 +3632,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,13 +3652,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,13 +3672,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3716,13 +3692,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3736,13 +3712,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3756,13 +3732,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3776,13 +3752,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3796,13 +3772,13 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3816,13 +3792,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3836,13 +3812,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3856,13 +3832,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3876,13 +3852,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3896,7 +3872,7 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>11</v>
@@ -3916,13 +3892,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3936,13 +3912,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3956,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3976,13 +3952,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3996,13 +3972,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4016,13 +3992,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4036,13 +4012,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4056,13 +4032,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4076,13 +4052,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4096,13 +4072,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4116,13 +4092,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4136,13 +4112,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4156,113 +4132,113 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4276,110 +4252,110 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -4387,59 +4363,59 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -4447,19 +4423,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -4467,59 +4443,59 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -4527,202 +4503,202 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>181</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="F107" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4736,50 +4712,50 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>241</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4787,22 +4763,22 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4816,613 +4792,613 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>181</v>
+        <v>234</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>184</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5436,13 +5412,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5456,13 +5432,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>244</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5476,13 +5452,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5496,510 +5472,510 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>31</v>
+        <v>307</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>31</v>
+        <v>307</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -6007,142 +5983,142 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6156,13 +6132,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>244</v>
+        <v>380</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6176,13 +6152,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>244</v>
+        <v>380</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>316</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6196,13 +6172,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>244</v>
+        <v>380</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>316</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6216,13 +6192,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>244</v>
+        <v>380</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6236,13 +6212,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>247</v>
+        <v>380</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6256,13 +6232,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>247</v>
+        <v>380</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6276,13 +6252,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>247</v>
+        <v>380</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6296,13 +6272,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>247</v>
+        <v>380</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6316,50 +6292,50 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>247</v>
+        <v>399</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>247</v>
+        <v>399</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -6367,39 +6343,39 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>247</v>
+        <v>399</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>247</v>
+        <v>399</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -6407,22 +6383,22 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6436,13 +6412,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6456,13 +6432,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6476,13 +6452,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6496,10 +6472,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -6516,113 +6492,113 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6636,30 +6612,30 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>18</v>
+        <v>433</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -6667,79 +6643,79 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>18</v>
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B208" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>443</v>
@@ -6747,82 +6723,82 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>453</v>
+        <v>26</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6836,13 +6812,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>453</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6856,13 +6832,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6876,13 +6852,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6896,13 +6872,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6916,13 +6892,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6936,13 +6912,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6956,113 +6932,113 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>31</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="E220" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F220" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>31</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>31</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>479</v>
+        <v>84</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7076,13 +7052,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>479</v>
+        <v>84</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7096,13 +7072,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>479</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7116,13 +7092,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7136,13 +7112,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7156,13 +7132,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>479</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7176,13 +7152,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -7196,13 +7172,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7216,7 +7192,7 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>11</v>
@@ -7236,10 +7212,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>5</v>
@@ -7256,10 +7232,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -7276,10 +7252,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>5</v>
@@ -7296,10 +7272,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -7316,10 +7292,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -7336,10 +7312,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>5</v>
@@ -7356,10 +7332,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>5</v>
@@ -7376,10 +7352,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>5</v>
@@ -7396,30 +7372,30 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="E242" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>5</v>
@@ -7427,19 +7403,19 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7447,19 +7423,19 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7467,22 +7443,22 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7496,13 +7472,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7516,10 +7492,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7527,19 +7503,19 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7547,62 +7523,62 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7616,13 +7592,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7636,13 +7612,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7656,93 +7632,93 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="E255" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7756,13 +7732,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7776,93 +7752,93 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>5</v>
+        <v>555</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>563</v>
+        <v>26</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7876,233 +7852,233 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C266" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="E266" s="1" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>181</v>
+        <v>11</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>88</v>
+        <v>575</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B273" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="E273" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>583</v>
+        <v>15</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -8116,13 +8092,13 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -8136,13 +8112,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -8156,13 +8132,13 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -8176,93 +8152,93 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>31</v>
+        <v>600</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>608</v>
+        <v>15</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8276,13 +8252,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8296,13 +8272,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8316,13 +8292,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8336,13 +8312,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8356,13 +8332,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8376,13 +8352,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8396,13 +8372,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8416,13 +8392,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8436,113 +8412,113 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="E294" s="1" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>184</v>
+        <v>11</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>187</v>
+        <v>31</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8556,13 +8532,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8576,13 +8552,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8596,13 +8572,13 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8616,113 +8592,113 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>637</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8736,13 +8712,13 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8756,13 +8732,13 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8776,13 +8752,13 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -8796,13 +8772,13 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -8816,193 +8792,193 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B313" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>656</v>
-      </c>
       <c r="E313" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>18</v>
+        <v>443</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>677</v>
-      </c>
       <c r="E318" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>453</v>
+        <v>84</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9016,13 +8992,13 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9036,93 +9012,93 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D324" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="E324" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -9136,13 +9112,13 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9156,193 +9132,113 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="E330" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D334" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="B334" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="E334" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A335" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="E335" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F335" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A336" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="E336" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F336" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A337" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="E337" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F337" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A338" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="E338" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
